--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="72">
   <si>
     <t>Profile</t>
   </si>
@@ -59,6 +59,9 @@
     <t/>
   </si>
   <si>
+    <t>null#82589-3</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>MII PR SDD Berufliche Stellung</t>
   </si>
   <si>
+    <t>null#67875-5</t>
+  </si>
+  <si>
     <t>CodeableConceptĵ</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
     <t>MII PR SDD Betreuungssituation</t>
   </si>
   <si>
+    <t>null#305060004</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-datenerhebung</t>
   </si>
   <si>
@@ -110,13 +119,16 @@
     <t>MII PR SDD Einkommen</t>
   </si>
   <si>
+    <t>null#98161-3</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-geburtsland-mutter</t>
   </si>
   <si>
     <t>MII PR SDD Geburtsland Mutter</t>
   </si>
   <si>
-    <t>null#246062003</t>
+    <t>null#63515-1</t>
   </si>
   <si>
     <t>mii-pr-sdd-geburtsland-vater</t>
@@ -125,12 +137,18 @@
     <t>MII PR SDD Geburtsland Vater</t>
   </si>
   <si>
+    <t>null#63492-3</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-haushaltsgroesse</t>
   </si>
   <si>
     <t>MII PR SDD Haushaltsgroesse</t>
   </si>
   <si>
+    <t>null#86639-2</t>
+  </si>
+  <si>
     <t>Quantityĵ</t>
   </si>
   <si>
@@ -149,24 +167,36 @@
     <t>MII PR SDD Partnerschaft</t>
   </si>
   <si>
+    <t>null#224083004</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-schulabschluss</t>
   </si>
   <si>
     <t>MII PR SDD Schulabschluss</t>
   </si>
   <si>
+    <t>null#276031006</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-schuljahre</t>
   </si>
   <si>
     <t>MII PR SDD Schuljahre</t>
   </si>
   <si>
+    <t>null#82590-1</t>
+  </si>
+  <si>
     <t>mii-pr-sdd-schwerbehindertenausweis</t>
   </si>
   <si>
     <t>MII PR SDD Schwerbehindertenausweis</t>
   </si>
   <si>
+    <t>null#101720-1</t>
+  </si>
+  <si>
     <t>MII CS SDD Schwerbehindertenausweis#gdb</t>
   </si>
   <si>
@@ -195,6 +225,9 @@
   </si>
   <si>
     <t>MII PR SDD Vertrauensperson</t>
+  </si>
+  <si>
+    <t>null#445091000124106</t>
   </si>
 </sst>
 </file>
@@ -380,19 +413,19 @@
         <v>14</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s" s="2">
         <v>14</v>
@@ -403,10 +436,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>13</v>
@@ -415,19 +448,19 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s" s="2">
         <v>14</v>
@@ -438,31 +471,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="F4" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="I4" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s" s="2">
         <v>14</v>
@@ -473,10 +506,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>13</v>
@@ -485,19 +518,19 @@
         <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s" s="2">
         <v>14</v>
@@ -508,10 +541,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -520,19 +553,19 @@
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>14</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s" s="2">
         <v>14</v>
@@ -543,10 +576,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -555,19 +588,19 @@
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s" s="2">
         <v>14</v>
@@ -578,10 +611,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -590,19 +623,19 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s" s="2">
         <v>14</v>
@@ -613,10 +646,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -625,19 +658,19 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s" s="2">
         <v>14</v>
@@ -648,10 +681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -660,19 +693,19 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>14</v>
@@ -683,10 +716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -698,16 +731,16 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>14</v>
@@ -718,10 +751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -730,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>14</v>
@@ -753,10 +786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -765,19 +798,19 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>14</v>
@@ -788,10 +821,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -800,19 +833,19 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>14</v>
@@ -823,10 +856,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -835,19 +868,19 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>14</v>
@@ -861,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -870,7 +903,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -879,10 +912,10 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>14</v>
@@ -896,7 +929,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -905,7 +938,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>14</v>
@@ -914,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>14</v>
@@ -931,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>14</v>
@@ -940,7 +973,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>14</v>
@@ -949,10 +982,10 @@
         <v>14</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>14</v>
@@ -966,7 +999,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>14</v>
@@ -975,7 +1008,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>14</v>
@@ -984,10 +1017,10 @@
         <v>14</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>14</v>
@@ -998,10 +1031,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1013,16 +1046,16 @@
         <v>14</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>14</v>
@@ -1033,10 +1066,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1045,19 +1078,19 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>14</v>
